--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MICHIGAN_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MICHIGAN_2019.xlsx
@@ -967,7 +967,7 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="35">
@@ -1723,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="77">
@@ -2173,7 +2173,7 @@
         <v>5</v>
       </c>
       <c r="D101">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="102">
@@ -2461,7 +2461,7 @@
         <v>5</v>
       </c>
       <c r="D117">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="118">
@@ -2497,7 +2497,7 @@
         <v>5</v>
       </c>
       <c r="D119">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="120">
@@ -2605,7 +2605,7 @@
         <v>5</v>
       </c>
       <c r="D125">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="126">
@@ -3181,7 +3181,7 @@
         <v>5</v>
       </c>
       <c r="D157">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="158">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C214">
@@ -4657,7 +4657,7 @@
         <v>5</v>
       </c>
       <c r="D239">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="240">
@@ -4765,7 +4765,7 @@
         <v>5</v>
       </c>
       <c r="D245">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="246">
@@ -5143,7 +5143,7 @@
         <v>5</v>
       </c>
       <c r="D266">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="267">
@@ -5305,7 +5305,7 @@
         <v>5</v>
       </c>
       <c r="D275">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="276">
@@ -5791,7 +5791,7 @@
         <v>5</v>
       </c>
       <c r="D302">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="303">
@@ -6133,7 +6133,7 @@
         <v>5</v>
       </c>
       <c r="D321">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="322">
@@ -7051,7 +7051,7 @@
         <v>5</v>
       </c>
       <c r="D372">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="373">
@@ -7537,7 +7537,7 @@
         <v>5</v>
       </c>
       <c r="D399">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="400">
@@ -8401,7 +8401,7 @@
         <v>5</v>
       </c>
       <c r="D447">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="448">
@@ -8491,7 +8491,7 @@
         <v>5</v>
       </c>
       <c r="D452">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="453">
@@ -8563,7 +8563,7 @@
         <v>5</v>
       </c>
       <c r="D456">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="457">
@@ -8617,7 +8617,7 @@
         <v>5</v>
       </c>
       <c r="D459">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="460">
@@ -8689,7 +8689,7 @@
         <v>5</v>
       </c>
       <c r="D463">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="464">
@@ -8815,7 +8815,7 @@
         <v>5</v>
       </c>
       <c r="D470">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="471">
@@ -9247,7 +9247,7 @@
         <v>5</v>
       </c>
       <c r="D494">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="495">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C518">
@@ -10590,14 +10590,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C569">
         <v>5</v>
       </c>
       <c r="D569">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="570">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C570">
@@ -11155,7 +11155,7 @@
         <v>5</v>
       </c>
       <c r="D600">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="601">
@@ -11497,7 +11497,7 @@
         <v>5</v>
       </c>
       <c r="D619">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="620">
@@ -11965,7 +11965,7 @@
         <v>5</v>
       </c>
       <c r="D645">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="646">
@@ -12937,7 +12937,7 @@
         <v>5</v>
       </c>
       <c r="D699">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="700">
@@ -13243,7 +13243,7 @@
         <v>5</v>
       </c>
       <c r="D716">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="717">
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="D725">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="726">
@@ -13459,7 +13459,7 @@
         <v>5</v>
       </c>
       <c r="D728">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="729">
@@ -13837,7 +13837,7 @@
         <v>5</v>
       </c>
       <c r="D749">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="750">
@@ -15205,7 +15205,7 @@
         <v>5</v>
       </c>
       <c r="D825">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="826">
@@ -15403,7 +15403,7 @@
         <v>5</v>
       </c>
       <c r="D836">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="837">
@@ -15745,7 +15745,7 @@
         <v>5</v>
       </c>
       <c r="D855">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="856">
@@ -15979,7 +15979,7 @@
         <v>5</v>
       </c>
       <c r="D868">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="869">
@@ -16123,7 +16123,7 @@
         <v>5</v>
       </c>
       <c r="D876">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="877">
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="D918">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="919">
@@ -17149,7 +17149,7 @@
         <v>5</v>
       </c>
       <c r="D933">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="934">
@@ -17167,7 +17167,7 @@
         <v>5</v>
       </c>
       <c r="D934">
-        <v>0.0009718172983479105</v>
+        <v>0.0009718172983479104</v>
       </c>
     </row>
     <row r="935">
